--- a/template/horaire.xlsx
+++ b/template/horaire.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11027"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10726"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/etiennerivard/notes_de_cours/bd2/template/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{448ED297-391E-6845-B5DF-AA00A0BD5CBD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B8D7649-C7E3-FB4F-89AB-FCA01038E435}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3000" yWindow="1920" windowWidth="27240" windowHeight="16440" xr2:uid="{4696F4E7-E751-AB46-8D30-A385E7EE1466}"/>
   </bookViews>
@@ -948,15 +948,27 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.59999389629810485"/>
+        <bgColor theme="4" tint="0.59999389629810485"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor theme="4" tint="0.79998168889431442"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -965,10 +977,29 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
+      <left style="thin">
+        <color theme="0"/>
+      </left>
+      <right style="thin">
+        <color theme="0"/>
+      </right>
       <top style="thin">
-        <color theme="5"/>
+        <color theme="0"/>
+      </top>
+      <bottom style="thin">
+        <color theme="0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="0"/>
+      </left>
+      <right style="thin">
+        <color theme="0"/>
+      </right>
+      <top style="thin">
+        <color theme="0"/>
       </top>
       <bottom/>
       <diagonal/>
@@ -977,7 +1008,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -986,7 +1017,9 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="22" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="0" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1333,7 +1366,7 @@
         <v>1</v>
       </c>
       <c r="C2" s="4">
-        <v>45525.552083333336</v>
+        <v>46254.635416666664</v>
       </c>
       <c r="D2" t="s">
         <v>8</v>
@@ -1349,8 +1382,8 @@
       <c r="B3">
         <v>2</v>
       </c>
-      <c r="C3" s="4">
-        <v>45530.34375</v>
+      <c r="C3" s="5">
+        <v>46259.427083333336</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>22</v>
@@ -1367,7 +1400,7 @@
         <v>3</v>
       </c>
       <c r="C4" s="4">
-        <v>45532.552083333336</v>
+        <v>46261.635416666664</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>35</v>
@@ -1383,8 +1416,8 @@
       <c r="B5">
         <v>4</v>
       </c>
-      <c r="C5" s="4">
-        <v>45540.34375</v>
+      <c r="C5" s="5">
+        <v>46266.427083333336</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>30</v>
@@ -1401,7 +1434,7 @@
         <v>5</v>
       </c>
       <c r="C6" s="4">
-        <v>45544.34375</v>
+        <v>46268.635416666664</v>
       </c>
       <c r="D6" s="3" t="s">
         <v>31</v>
@@ -1417,8 +1450,8 @@
       <c r="B7">
         <v>6</v>
       </c>
-      <c r="C7" s="4">
-        <v>45546.552083333336</v>
+      <c r="C7" s="5">
+        <v>46276.427083333336</v>
       </c>
       <c r="D7" t="s">
         <v>9</v>
@@ -1435,7 +1468,7 @@
         <v>7</v>
       </c>
       <c r="C8" s="4">
-        <v>45551.34375</v>
+        <v>46280.427083333336</v>
       </c>
       <c r="D8" t="s">
         <v>20</v>
@@ -1448,8 +1481,8 @@
       <c r="B9">
         <v>8</v>
       </c>
-      <c r="C9" s="4">
-        <v>45553.552083333336</v>
+      <c r="C9" s="5">
+        <v>46282.635416666664</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>32</v>
@@ -1466,7 +1499,7 @@
         <v>9</v>
       </c>
       <c r="C10" s="4">
-        <v>45558.34375</v>
+        <v>46287.427083333336</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>38</v>
@@ -1482,8 +1515,8 @@
       <c r="B11">
         <v>10</v>
       </c>
-      <c r="C11" s="4">
-        <v>45560.552083333336</v>
+      <c r="C11" s="5">
+        <v>46289.635416666664</v>
       </c>
       <c r="D11" t="s">
         <v>33</v>
@@ -1500,7 +1533,7 @@
         <v>11</v>
       </c>
       <c r="C12" s="4">
-        <v>45565.34375</v>
+        <v>46294.427083333336</v>
       </c>
       <c r="D12" t="s">
         <v>10</v>
@@ -1516,8 +1549,8 @@
       <c r="B13">
         <v>12</v>
       </c>
-      <c r="C13" s="4">
-        <v>45567.552083333336</v>
+      <c r="C13" s="5">
+        <v>46296.635416666664</v>
       </c>
       <c r="D13" t="s">
         <v>11</v>
@@ -1531,7 +1564,7 @@
         <v>13</v>
       </c>
       <c r="C14" s="4">
-        <v>45572.34375</v>
+        <v>46301.427083333336</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>41</v>
@@ -1547,8 +1580,8 @@
       <c r="B15">
         <v>14</v>
       </c>
-      <c r="C15" s="4">
-        <v>45574.552083333336</v>
+      <c r="C15" s="5">
+        <v>46303.635416666664</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>12</v>
@@ -1565,7 +1598,7 @@
         <v>15</v>
       </c>
       <c r="C16" s="4">
-        <v>45586.34375</v>
+        <v>46315.427083333336</v>
       </c>
       <c r="D16" s="2" t="s">
         <v>42</v>
@@ -1581,8 +1614,8 @@
       <c r="B17">
         <v>16</v>
       </c>
-      <c r="C17" s="4">
-        <v>45588.552083333336</v>
+      <c r="C17" s="5">
+        <v>46317.635416666664</v>
       </c>
       <c r="D17" t="s">
         <v>13</v>
@@ -1599,7 +1632,7 @@
         <v>17</v>
       </c>
       <c r="C18" s="4">
-        <v>45593.34375</v>
+        <v>46322.427083333336</v>
       </c>
       <c r="D18" t="s">
         <v>13</v>
@@ -1615,8 +1648,8 @@
       <c r="B19">
         <v>18</v>
       </c>
-      <c r="C19" s="4">
-        <v>45595.552083333336</v>
+      <c r="C19" s="5">
+        <v>46324.635416666664</v>
       </c>
       <c r="D19" s="2" t="s">
         <v>37</v>
@@ -1633,7 +1666,7 @@
         <v>19</v>
       </c>
       <c r="C20" s="4">
-        <v>45600.34375</v>
+        <v>46329.427083333336</v>
       </c>
       <c r="D20" t="s">
         <v>21</v>
@@ -1647,8 +1680,8 @@
       <c r="B21">
         <v>20</v>
       </c>
-      <c r="C21" s="4">
-        <v>45604.552083333336</v>
+      <c r="C21" s="5">
+        <v>46331.635416666664</v>
       </c>
       <c r="D21" t="s">
         <v>14</v>
@@ -1662,7 +1695,7 @@
         <v>21</v>
       </c>
       <c r="C22" s="4">
-        <v>45607.34375</v>
+        <v>46338.635416666664</v>
       </c>
       <c r="D22" t="s">
         <v>14</v>
@@ -1675,8 +1708,8 @@
       <c r="B23">
         <v>22</v>
       </c>
-      <c r="C23" s="4">
-        <v>45609.552083333336</v>
+      <c r="C23" s="5">
+        <v>46343.427083333336</v>
       </c>
       <c r="D23" t="s">
         <v>14</v>
@@ -1690,7 +1723,7 @@
         <v>23</v>
       </c>
       <c r="C24" s="4">
-        <v>45614.34375</v>
+        <v>46345.635416666664</v>
       </c>
       <c r="D24" t="s">
         <v>14</v>
@@ -1703,8 +1736,8 @@
       <c r="B25">
         <v>24</v>
       </c>
-      <c r="C25" s="4">
-        <v>45616.552083333336</v>
+      <c r="C25" s="5">
+        <v>46350.427083333336</v>
       </c>
       <c r="D25" t="s">
         <v>43</v>
@@ -1718,7 +1751,7 @@
         <v>25</v>
       </c>
       <c r="C26" s="4">
-        <v>45621.34375</v>
+        <v>46352.635416666664</v>
       </c>
       <c r="D26" t="s">
         <v>15</v>
@@ -1731,8 +1764,8 @@
       <c r="B27">
         <v>26</v>
       </c>
-      <c r="C27" s="4">
-        <v>45623.552083333336</v>
+      <c r="C27" s="5">
+        <v>46357.427083333336</v>
       </c>
       <c r="D27" t="s">
         <v>16</v>
@@ -1746,7 +1779,7 @@
         <v>27</v>
       </c>
       <c r="C28" s="4">
-        <v>45628.34375</v>
+        <v>46359.635416666664</v>
       </c>
       <c r="D28" t="s">
         <v>17</v>
@@ -1759,8 +1792,8 @@
       <c r="B29">
         <v>28</v>
       </c>
-      <c r="C29" s="4">
-        <v>45630.552083333336</v>
+      <c r="C29" s="5">
+        <v>46364.427083333336</v>
       </c>
       <c r="D29" t="s">
         <v>39</v>
@@ -1774,7 +1807,7 @@
         <v>29</v>
       </c>
       <c r="C30" s="4">
-        <v>45635.34375</v>
+        <v>46366.635416666664</v>
       </c>
       <c r="D30" t="s">
         <v>18</v>
@@ -1787,8 +1820,8 @@
       <c r="B31">
         <v>30</v>
       </c>
-      <c r="C31" s="4">
-        <v>45637.552083333336</v>
+      <c r="C31" s="6">
+        <v>46371.427083333336</v>
       </c>
       <c r="D31" t="s">
         <v>19</v>
